--- a/nr-update-patient-name/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/nr-update-patient-name/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4224" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5018" uniqueCount="555">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T13:41:02+00:00</t>
+    <t>2025-02-17T10:02:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1087,16 +1087,40 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>Practitioner.identifier:idNatPs.type.id</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:idNatPs.type.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:idNatPs.type.coding</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:idNatPs.type.coding.id</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:idNatPs.type.coding.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:idNatPs.type.coding.system</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:idNatPs.type.coding.version</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:idNatPs.type.coding.code</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:idNatPs.type.coding.display</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:idNatPs.type.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:idNatPs.type.text</t>
   </si>
   <si>
     <t>Practitioner.identifier:idNatPs.system</t>
-  </si>
-  <si>
-    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
   </si>
   <si>
     <t>urn:oid:1.2.250.1.71.4.2.1</t>
@@ -1142,6 +1166,39 @@
     &lt;code value="RPPS"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:rpps.type.id</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:rpps.type.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:rpps.type.coding</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:rpps.type.coding.id</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:rpps.type.coding.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:rpps.type.coding.system</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:rpps.type.coding.version</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:rpps.type.coding.code</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:rpps.type.coding.display</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:rpps.type.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:rpps.type.text</t>
   </si>
   <si>
     <t>Practitioner.identifier:rpps.system</t>
@@ -1995,7 +2052,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN116"/>
+  <dimension ref="A1:AN138"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="65.296875" customWidth="true" bestFit="true"/>
@@ -7130,11 +7187,9 @@
       <c r="X45" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="Y45" t="s" s="2">
-        <v>344</v>
-      </c>
+      <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
-        <v>345</v>
+        <v>237</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>78</v>
@@ -7181,10 +7236,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>299</v>
+        <v>240</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7192,7 +7247,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>89</v>
@@ -7204,23 +7259,19 @@
         <v>78</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>300</v>
+        <v>104</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>303</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>78</v>
       </c>
@@ -7229,10 +7280,10 @@
         <v>78</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>348</v>
+        <v>78</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>304</v>
+        <v>78</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>78</v>
@@ -7268,7 +7319,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>305</v>
+        <v>106</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7280,16 +7331,16 @@
         <v>78</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>306</v>
+        <v>78</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>307</v>
+        <v>107</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>308</v>
+        <v>78</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>78</v>
@@ -7297,21 +7348,21 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>309</v>
+        <v>241</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>78</v>
@@ -7320,19 +7371,19 @@
         <v>78</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>350</v>
+        <v>111</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>311</v>
+        <v>112</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>312</v>
+        <v>113</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7346,7 +7397,7 @@
         <v>78</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>313</v>
+        <v>78</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>78</v>
@@ -7370,40 +7421,40 @@
         <v>78</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>314</v>
+        <v>117</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>315</v>
+        <v>78</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>316</v>
+        <v>107</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>317</v>
+        <v>78</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>78</v>
@@ -7411,10 +7462,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>318</v>
+        <v>242</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7425,7 +7476,7 @@
         <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>78</v>
@@ -7437,16 +7488,20 @@
         <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>319</v>
+        <v>147</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>320</v>
+        <v>243</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>78</v>
       </c>
@@ -7494,13 +7549,13 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>322</v>
+        <v>247</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>78</v>
@@ -7509,13 +7564,13 @@
         <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>323</v>
+        <v>248</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>324</v>
+        <v>249</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>325</v>
+        <v>78</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>78</v>
@@ -7523,10 +7578,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>326</v>
+        <v>250</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7546,20 +7601,18 @@
         <v>78</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>327</v>
+        <v>103</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>328</v>
+        <v>104</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>78</v>
@@ -7608,7 +7661,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>331</v>
+        <v>106</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7620,16 +7673,16 @@
         <v>78</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>332</v>
+        <v>78</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>333</v>
+        <v>107</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>334</v>
+        <v>78</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>78</v>
@@ -7637,16 +7690,14 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="C50" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7662,21 +7713,21 @@
         <v>78</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>209</v>
+        <v>110</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>355</v>
+        <v>111</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>78</v>
       </c>
@@ -7712,19 +7763,19 @@
         <v>78</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>208</v>
+        <v>117</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7736,27 +7787,27 @@
         <v>78</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>215</v>
+        <v>78</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>216</v>
+        <v>107</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>217</v>
+        <v>78</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>218</v>
+        <v>78</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>219</v>
+        <v>252</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7776,19 +7827,23 @@
         <v>78</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>104</v>
+        <v>253</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>256</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>78</v>
       </c>
@@ -7800,7 +7855,7 @@
         <v>78</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>78</v>
+        <v>257</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>78</v>
@@ -7836,7 +7891,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>106</v>
+        <v>258</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7848,13 +7903,13 @@
         <v>78</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>78</v>
+        <v>259</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>107</v>
+        <v>260</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>78</v>
@@ -7865,21 +7920,21 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>220</v>
+        <v>261</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>78</v>
@@ -7888,19 +7943,19 @@
         <v>78</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>111</v>
+        <v>262</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>112</v>
+        <v>263</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>113</v>
+        <v>264</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7938,37 +7993,37 @@
         <v>78</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>117</v>
+        <v>265</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>78</v>
+        <v>266</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>107</v>
+        <v>267</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>78</v>
@@ -7979,10 +8034,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>221</v>
+        <v>268</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7999,7 +8054,7 @@
         <v>78</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J53" t="s" s="2">
         <v>90</v>
@@ -8008,16 +8063,14 @@
         <v>169</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>222</v>
+        <v>269</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>224</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>225</v>
+        <v>271</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -8042,13 +8095,13 @@
         <v>78</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>226</v>
+        <v>78</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>227</v>
+        <v>78</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>228</v>
+        <v>78</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>78</v>
@@ -8066,7 +8119,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>229</v>
+        <v>272</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8081,10 +8134,10 @@
         <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>192</v>
+        <v>273</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>230</v>
+        <v>274</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>78</v>
@@ -8095,10 +8148,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>231</v>
+        <v>275</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8106,7 +8159,7 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>89</v>
@@ -8121,19 +8174,17 @@
         <v>90</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>232</v>
+        <v>103</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>233</v>
+        <v>276</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>235</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>236</v>
+        <v>278</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>78</v>
@@ -8143,7 +8194,7 @@
         <v>78</v>
       </c>
       <c r="S54" t="s" s="2">
-        <v>360</v>
+        <v>78</v>
       </c>
       <c r="T54" t="s" s="2">
         <v>78</v>
@@ -8158,13 +8209,13 @@
         <v>78</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>151</v>
+        <v>78</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>344</v>
+        <v>78</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>345</v>
+        <v>78</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>78</v>
@@ -8182,7 +8233,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>238</v>
+        <v>279</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8197,10 +8248,10 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>239</v>
+        <v>280</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>230</v>
+        <v>281</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>78</v>
@@ -8211,10 +8262,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8222,7 +8273,7 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>89</v>
@@ -8237,19 +8288,19 @@
         <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>131</v>
+        <v>283</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>300</v>
+        <v>284</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>347</v>
+        <v>285</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>303</v>
+        <v>287</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>78</v>
@@ -8259,10 +8310,10 @@
         <v>78</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>362</v>
+        <v>78</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>304</v>
+        <v>78</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>78</v>
@@ -8298,7 +8349,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>305</v>
+        <v>288</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8313,13 +8364,13 @@
         <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>307</v>
+        <v>290</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>308</v>
+        <v>78</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>78</v>
@@ -8327,10 +8378,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>309</v>
+        <v>291</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8338,7 +8389,7 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>89</v>
@@ -8356,15 +8407,17 @@
         <v>103</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>310</v>
+        <v>292</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>311</v>
+        <v>293</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>78</v>
       </c>
@@ -8376,7 +8429,7 @@
         <v>78</v>
       </c>
       <c r="T56" t="s" s="2">
-        <v>313</v>
+        <v>78</v>
       </c>
       <c r="U56" t="s" s="2">
         <v>78</v>
@@ -8412,7 +8465,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>314</v>
+        <v>296</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8427,13 +8480,13 @@
         <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>315</v>
+        <v>297</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>316</v>
+        <v>298</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>317</v>
+        <v>78</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>78</v>
@@ -8441,10 +8494,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>318</v>
+        <v>299</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8452,7 +8505,7 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>89</v>
@@ -8467,16 +8520,20 @@
         <v>90</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>319</v>
+        <v>131</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>303</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>78</v>
       </c>
@@ -8485,10 +8542,10 @@
         <v>78</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>78</v>
+        <v>356</v>
       </c>
       <c r="T57" t="s" s="2">
-        <v>78</v>
+        <v>304</v>
       </c>
       <c r="U57" t="s" s="2">
         <v>78</v>
@@ -8524,7 +8581,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>322</v>
+        <v>305</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8539,13 +8596,13 @@
         <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>323</v>
+        <v>306</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>325</v>
+        <v>308</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>78</v>
@@ -8553,10 +8610,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>326</v>
+        <v>309</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8564,7 +8621,7 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>89</v>
@@ -8579,16 +8636,16 @@
         <v>90</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>327</v>
+        <v>103</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>328</v>
+        <v>358</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>329</v>
+        <v>311</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>330</v>
+        <v>312</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8602,7 +8659,7 @@
         <v>78</v>
       </c>
       <c r="T58" t="s" s="2">
-        <v>78</v>
+        <v>313</v>
       </c>
       <c r="U58" t="s" s="2">
         <v>78</v>
@@ -8638,7 +8695,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8653,13 +8710,13 @@
         <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>333</v>
+        <v>316</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>334</v>
+        <v>317</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>78</v>
@@ -8667,10 +8724,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>366</v>
+        <v>318</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8693,26 +8750,20 @@
         <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>283</v>
+        <v>319</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>367</v>
+        <v>320</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>370</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q59" t="s" s="2">
-        <v>371</v>
-      </c>
+      <c r="Q59" s="2"/>
       <c r="R59" t="s" s="2">
         <v>78</v>
       </c>
@@ -8756,7 +8807,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>366</v>
+        <v>322</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8771,24 +8822,24 @@
         <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>78</v>
+        <v>323</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>372</v>
+        <v>324</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>78</v>
+        <v>325</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>373</v>
+        <v>78</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>374</v>
+        <v>360</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>374</v>
+        <v>326</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8799,7 +8850,7 @@
         <v>79</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>78</v>
@@ -8811,20 +8862,18 @@
         <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>375</v>
+        <v>327</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>376</v>
+        <v>328</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>377</v>
+        <v>329</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>379</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>78</v>
       </c>
@@ -8872,13 +8921,13 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>374</v>
+        <v>331</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>78</v>
@@ -8887,13 +8936,13 @@
         <v>101</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>380</v>
+        <v>332</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>381</v>
+        <v>333</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>382</v>
+        <v>334</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>78</v>
@@ -8901,12 +8950,14 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>383</v>
+        <v>361</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="C61" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="C61" t="s" s="2">
+        <v>362</v>
+      </c>
       <c r="D61" t="s" s="2">
         <v>78</v>
       </c>
@@ -8927,19 +8978,17 @@
         <v>90</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>384</v>
+        <v>209</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>385</v>
+        <v>363</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>387</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>388</v>
+        <v>212</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>78</v>
@@ -8988,7 +9037,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>383</v>
+        <v>208</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9003,24 +9052,24 @@
         <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>389</v>
+        <v>215</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>390</v>
+        <v>216</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>391</v>
+        <v>217</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>78</v>
+        <v>218</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>392</v>
+        <v>364</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>392</v>
+        <v>219</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9031,7 +9080,7 @@
         <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>78</v>
@@ -9040,23 +9089,19 @@
         <v>78</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>393</v>
+        <v>103</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>394</v>
+        <v>104</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>397</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>78</v>
       </c>
@@ -9104,28 +9149,28 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>392</v>
+        <v>106</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>398</v>
+        <v>78</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>399</v>
+        <v>107</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>400</v>
+        <v>78</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>78</v>
@@ -9133,21 +9178,21 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>401</v>
+        <v>365</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>401</v>
+        <v>220</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>78</v>
@@ -9156,21 +9201,21 @@
         <v>78</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>169</v>
+        <v>110</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>402</v>
+        <v>111</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" t="s" s="2">
-        <v>404</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>78</v>
       </c>
@@ -9194,52 +9239,52 @@
         <v>78</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>226</v>
+        <v>78</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>405</v>
+        <v>78</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>406</v>
+        <v>78</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>401</v>
+        <v>117</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>407</v>
+        <v>78</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>408</v>
+        <v>107</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>409</v>
+        <v>78</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>78</v>
@@ -9247,10 +9292,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>410</v>
+        <v>366</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>410</v>
+        <v>221</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9267,23 +9312,25 @@
         <v>78</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J64" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>411</v>
+        <v>169</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>412</v>
+        <v>222</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>223</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="O64" t="s" s="2">
-        <v>414</v>
+        <v>225</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>78</v>
@@ -9308,13 +9355,13 @@
         <v>78</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>78</v>
+        <v>226</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>78</v>
+        <v>227</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>78</v>
+        <v>228</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>78</v>
@@ -9332,7 +9379,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>410</v>
+        <v>229</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9347,13 +9394,13 @@
         <v>101</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>415</v>
+        <v>192</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>416</v>
+        <v>230</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>417</v>
+        <v>78</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>78</v>
@@ -9361,10 +9408,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>418</v>
+        <v>367</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>418</v>
+        <v>231</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9372,10 +9419,10 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>78</v>
@@ -9384,20 +9431,22 @@
         <v>78</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>419</v>
+        <v>232</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>420</v>
+        <v>233</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>235</v>
+      </c>
       <c r="O65" t="s" s="2">
-        <v>422</v>
+        <v>236</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>78</v>
@@ -9407,7 +9456,7 @@
         <v>78</v>
       </c>
       <c r="S65" t="s" s="2">
-        <v>78</v>
+        <v>368</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>78</v>
@@ -9422,13 +9471,11 @@
         <v>78</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="Y65" s="2"/>
       <c r="Z65" t="s" s="2">
-        <v>78</v>
+        <v>237</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>78</v>
@@ -9446,13 +9493,13 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>418</v>
+        <v>238</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>78</v>
@@ -9461,13 +9508,13 @@
         <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>78</v>
+        <v>239</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>423</v>
+        <v>230</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>424</v>
+        <v>78</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>78</v>
@@ -9475,10 +9522,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>425</v>
+        <v>369</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>425</v>
+        <v>240</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9489,7 +9536,7 @@
         <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>78</v>
@@ -9501,13 +9548,13 @@
         <v>78</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>426</v>
+        <v>103</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>427</v>
+        <v>104</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>428</v>
+        <v>105</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9546,38 +9593,40 @@
         <v>78</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="AC66" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>425</v>
+        <v>106</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>430</v>
+        <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>431</v>
+        <v>107</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>432</v>
+        <v>78</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>78</v>
@@ -9585,21 +9634,21 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>433</v>
+        <v>370</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>433</v>
+        <v>241</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>78</v>
@@ -9611,15 +9660,17 @@
         <v>78</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>78</v>
@@ -9656,31 +9707,31 @@
         <v>78</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>78</v>
@@ -9697,14 +9748,14 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>434</v>
+        <v>371</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>434</v>
+        <v>242</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9720,21 +9771,23 @@
         <v>78</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>111</v>
+        <v>243</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>112</v>
+        <v>244</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O68" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>78</v>
       </c>
@@ -9782,7 +9835,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>117</v>
+        <v>247</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9794,13 +9847,13 @@
         <v>78</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>78</v>
+        <v>248</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>107</v>
+        <v>249</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>78</v>
@@ -9811,46 +9864,42 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>435</v>
+        <v>372</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>435</v>
+        <v>250</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>436</v>
+        <v>78</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>437</v>
+        <v>104</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>206</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>78</v>
       </c>
@@ -9898,25 +9947,25 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>439</v>
+        <v>106</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>192</v>
+        <v>107</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>78</v>
@@ -9927,14 +9976,14 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>440</v>
+        <v>373</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>440</v>
+        <v>251</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -9953,18 +10002,18 @@
         <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>209</v>
+        <v>110</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>441</v>
+        <v>111</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N70" s="2"/>
-      <c r="O70" t="s" s="2">
-        <v>443</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>78</v>
       </c>
@@ -10000,19 +10049,19 @@
         <v>78</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>440</v>
+        <v>117</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10024,13 +10073,13 @@
         <v>78</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>444</v>
+        <v>107</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>78</v>
@@ -10041,10 +10090,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>445</v>
+        <v>374</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>445</v>
+        <v>252</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10052,7 +10101,7 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>89</v>
@@ -10064,19 +10113,23 @@
         <v>78</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>232</v>
+        <v>131</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>446</v>
+        <v>253</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>256</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
       </c>
@@ -10088,7 +10141,7 @@
         <v>78</v>
       </c>
       <c r="T71" t="s" s="2">
-        <v>78</v>
+        <v>257</v>
       </c>
       <c r="U71" t="s" s="2">
         <v>78</v>
@@ -10100,13 +10153,13 @@
         <v>78</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>448</v>
+        <v>78</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>449</v>
+        <v>78</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>78</v>
@@ -10124,10 +10177,10 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>445</v>
+        <v>258</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>89</v>
@@ -10139,13 +10192,13 @@
         <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>78</v>
+        <v>259</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>431</v>
+        <v>260</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>450</v>
+        <v>78</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>78</v>
@@ -10153,10 +10206,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>451</v>
+        <v>375</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>451</v>
+        <v>261</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10176,21 +10229,21 @@
         <v>78</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>319</v>
+        <v>103</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>452</v>
+        <v>262</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N72" s="2"/>
-      <c r="O72" t="s" s="2">
-        <v>454</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>78</v>
       </c>
@@ -10238,7 +10291,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>451</v>
+        <v>265</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10253,13 +10306,13 @@
         <v>101</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>78</v>
+        <v>266</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>455</v>
+        <v>267</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>456</v>
+        <v>78</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>78</v>
@@ -10267,10 +10320,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>457</v>
+        <v>376</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>457</v>
+        <v>268</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10290,19 +10343,21 @@
         <v>78</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>327</v>
+        <v>169</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>458</v>
+        <v>269</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>459</v>
+        <v>270</v>
       </c>
       <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
+      <c r="O73" t="s" s="2">
+        <v>271</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>78</v>
       </c>
@@ -10350,7 +10405,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>457</v>
+        <v>272</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10365,10 +10420,10 @@
         <v>101</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>78</v>
+        <v>273</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>460</v>
+        <v>274</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>78</v>
@@ -10379,14 +10434,12 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>461</v>
+        <v>377</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="C74" t="s" s="2">
-        <v>462</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
         <v>78</v>
       </c>
@@ -10395,7 +10448,7 @@
         <v>79</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>78</v>
@@ -10404,19 +10457,21 @@
         <v>78</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>426</v>
+        <v>103</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>463</v>
+        <v>276</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>428</v>
+        <v>277</v>
       </c>
       <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
+      <c r="O74" t="s" s="2">
+        <v>278</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>78</v>
       </c>
@@ -10464,13 +10519,13 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>425</v>
+        <v>279</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>78</v>
@@ -10479,13 +10534,13 @@
         <v>101</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>430</v>
+        <v>280</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>431</v>
+        <v>281</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>432</v>
+        <v>78</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>78</v>
@@ -10493,10 +10548,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>464</v>
+        <v>378</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>433</v>
+        <v>282</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10516,19 +10571,23 @@
         <v>78</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>103</v>
+        <v>283</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>104</v>
+        <v>284</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N75" s="2"/>
-      <c r="O75" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="P75" t="s" s="2">
         <v>78</v>
       </c>
@@ -10576,7 +10635,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>106</v>
+        <v>288</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10588,13 +10647,13 @@
         <v>78</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>78</v>
+        <v>289</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>107</v>
+        <v>290</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>78</v>
@@ -10605,21 +10664,21 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>465</v>
+        <v>379</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>434</v>
+        <v>291</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>78</v>
@@ -10628,21 +10687,23 @@
         <v>78</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>111</v>
+        <v>292</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>112</v>
+        <v>293</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O76" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>78</v>
       </c>
@@ -10690,25 +10751,25 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>117</v>
+        <v>296</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>78</v>
+        <v>297</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>107</v>
+        <v>298</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>78</v>
@@ -10719,45 +10780,45 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>466</v>
+        <v>380</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>435</v>
+        <v>299</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>436</v>
+        <v>78</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J77" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>437</v>
+        <v>300</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>438</v>
+        <v>301</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>113</v>
+        <v>302</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>206</v>
+        <v>303</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>78</v>
@@ -10767,10 +10828,10 @@
         <v>78</v>
       </c>
       <c r="S77" t="s" s="2">
-        <v>78</v>
+        <v>381</v>
       </c>
       <c r="T77" t="s" s="2">
-        <v>78</v>
+        <v>304</v>
       </c>
       <c r="U77" t="s" s="2">
         <v>78</v>
@@ -10806,28 +10867,28 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>439</v>
+        <v>305</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>78</v>
+        <v>306</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>192</v>
+        <v>307</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>78</v>
+        <v>308</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>78</v>
@@ -10835,10 +10896,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>467</v>
+        <v>382</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>440</v>
+        <v>309</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10846,10 +10907,10 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>78</v>
@@ -10858,21 +10919,21 @@
         <v>78</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>209</v>
+        <v>103</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>441</v>
+        <v>310</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N78" s="2"/>
-      <c r="O78" t="s" s="2">
-        <v>443</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>78</v>
       </c>
@@ -10884,7 +10945,7 @@
         <v>78</v>
       </c>
       <c r="T78" t="s" s="2">
-        <v>78</v>
+        <v>313</v>
       </c>
       <c r="U78" t="s" s="2">
         <v>78</v>
@@ -10920,13 +10981,13 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>440</v>
+        <v>314</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>78</v>
@@ -10935,13 +10996,13 @@
         <v>101</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>78</v>
+        <v>315</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>444</v>
+        <v>316</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>78</v>
+        <v>317</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>78</v>
@@ -10949,10 +11010,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>468</v>
+        <v>383</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>445</v>
+        <v>318</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10960,7 +11021,7 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G79" t="s" s="2">
         <v>89</v>
@@ -10972,16 +11033,16 @@
         <v>78</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>232</v>
+        <v>319</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>446</v>
+        <v>320</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>447</v>
+        <v>321</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11008,13 +11069,13 @@
         <v>78</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>448</v>
+        <v>78</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>449</v>
+        <v>78</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>78</v>
@@ -11032,10 +11093,10 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>445</v>
+        <v>322</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH79" t="s" s="2">
         <v>89</v>
@@ -11047,13 +11108,13 @@
         <v>101</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>78</v>
+        <v>323</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>431</v>
+        <v>324</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>450</v>
+        <v>325</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>78</v>
@@ -11061,10 +11122,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>469</v>
+        <v>384</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>470</v>
+        <v>326</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11084,18 +11145,20 @@
         <v>78</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>103</v>
+        <v>327</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>104</v>
+        <v>328</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N80" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>78</v>
@@ -11144,7 +11207,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>106</v>
+        <v>331</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11156,16 +11219,16 @@
         <v>78</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>78</v>
+        <v>332</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>107</v>
+        <v>333</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>78</v>
+        <v>334</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>78</v>
@@ -11173,21 +11236,21 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>471</v>
+        <v>385</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>472</v>
+        <v>385</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>78</v>
@@ -11196,25 +11259,29 @@
         <v>78</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>110</v>
+        <v>283</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>111</v>
+        <v>386</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>112</v>
+        <v>387</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O81" s="2"/>
+        <v>388</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>389</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q81" s="2"/>
+      <c r="Q81" t="s" s="2">
+        <v>390</v>
+      </c>
       <c r="R81" t="s" s="2">
         <v>78</v>
       </c>
@@ -11246,51 +11313,51 @@
         <v>78</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>117</v>
+        <v>385</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>107</v>
+        <v>391</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>78</v>
+        <v>392</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>473</v>
+        <v>393</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>474</v>
+        <v>393</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11313,19 +11380,19 @@
         <v>90</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>147</v>
+        <v>394</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>243</v>
+        <v>395</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>244</v>
+        <v>396</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>245</v>
+        <v>397</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>246</v>
+        <v>398</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>78</v>
@@ -11362,17 +11429,19 @@
         <v>78</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AC82" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>475</v>
+        <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>247</v>
+        <v>393</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -11387,13 +11456,13 @@
         <v>101</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>248</v>
+        <v>399</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>249</v>
+        <v>400</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>78</v>
+        <v>401</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>78</v>
@@ -11401,14 +11470,12 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>476</v>
+        <v>402</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="C83" t="s" s="2">
-        <v>477</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
         <v>78</v>
       </c>
@@ -11417,7 +11484,7 @@
         <v>79</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>78</v>
@@ -11429,19 +11496,19 @@
         <v>90</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>147</v>
+        <v>403</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>243</v>
+        <v>404</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>244</v>
+        <v>405</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>245</v>
+        <v>406</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>246</v>
+        <v>407</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>78</v>
@@ -11466,11 +11533,13 @@
         <v>78</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y83" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z83" t="s" s="2">
-        <v>478</v>
+        <v>78</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>78</v>
@@ -11488,7 +11557,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>247</v>
+        <v>402</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -11503,13 +11572,13 @@
         <v>101</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>248</v>
+        <v>408</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>249</v>
+        <v>409</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>78</v>
+        <v>410</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>78</v>
@@ -11517,14 +11586,12 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>479</v>
+        <v>411</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="C84" t="s" s="2">
-        <v>462</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
         <v>78</v>
       </c>
@@ -11533,7 +11600,7 @@
         <v>79</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>78</v>
@@ -11545,19 +11612,19 @@
         <v>90</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>147</v>
+        <v>412</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>243</v>
+        <v>413</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>244</v>
+        <v>414</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>245</v>
+        <v>415</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>246</v>
+        <v>416</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>78</v>
@@ -11582,11 +11649,13 @@
         <v>78</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y84" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z84" t="s" s="2">
-        <v>480</v>
+        <v>78</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>78</v>
@@ -11604,7 +11673,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>247</v>
+        <v>411</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -11619,13 +11688,13 @@
         <v>101</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>248</v>
+        <v>417</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>249</v>
+        <v>418</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>78</v>
+        <v>419</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>78</v>
@@ -11633,10 +11702,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>481</v>
+        <v>420</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>482</v>
+        <v>420</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11659,19 +11728,17 @@
         <v>90</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>103</v>
+        <v>169</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>292</v>
+        <v>421</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>294</v>
-      </c>
+        <v>422</v>
+      </c>
+      <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
-        <v>295</v>
+        <v>423</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>78</v>
@@ -11696,13 +11763,13 @@
         <v>78</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>78</v>
+        <v>226</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>78</v>
+        <v>424</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>78</v>
+        <v>425</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>78</v>
@@ -11720,7 +11787,7 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>296</v>
+        <v>420</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -11735,13 +11802,13 @@
         <v>101</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>297</v>
+        <v>426</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>298</v>
+        <v>427</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>78</v>
+        <v>428</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>78</v>
@@ -11749,10 +11816,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>483</v>
+        <v>429</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>451</v>
+        <v>429</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11772,20 +11839,20 @@
         <v>78</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>319</v>
+        <v>430</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>452</v>
+        <v>431</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>453</v>
+        <v>432</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
-        <v>454</v>
+        <v>433</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>78</v>
@@ -11834,7 +11901,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>451</v>
+        <v>429</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -11849,13 +11916,13 @@
         <v>101</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>78</v>
+        <v>434</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>455</v>
+        <v>435</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>78</v>
@@ -11863,10 +11930,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>484</v>
+        <v>437</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>457</v>
+        <v>437</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11877,7 +11944,7 @@
         <v>79</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>78</v>
@@ -11889,16 +11956,18 @@
         <v>78</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>327</v>
+        <v>438</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>458</v>
+        <v>439</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>459</v>
+        <v>440</v>
       </c>
       <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
+      <c r="O87" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>78</v>
       </c>
@@ -11946,13 +12015,13 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>457</v>
+        <v>437</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>78</v>
@@ -11964,10 +12033,10 @@
         <v>78</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>460</v>
+        <v>442</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>78</v>
+        <v>443</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>78</v>
@@ -11975,14 +12044,12 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>485</v>
+        <v>444</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="C88" t="s" s="2">
-        <v>486</v>
-      </c>
+        <v>444</v>
+      </c>
+      <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
         <v>78</v>
       </c>
@@ -11991,7 +12058,7 @@
         <v>79</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>78</v>
@@ -12003,13 +12070,13 @@
         <v>78</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>426</v>
+        <v>445</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>487</v>
+        <v>446</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>428</v>
+        <v>447</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12048,19 +12115,17 @@
         <v>78</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>448</v>
+      </c>
+      <c r="AC88" s="2"/>
       <c r="AD88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>425</v>
+        <v>444</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12075,13 +12140,13 @@
         <v>101</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>430</v>
+        <v>449</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>431</v>
+        <v>450</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>432</v>
+        <v>451</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>78</v>
@@ -12089,10 +12154,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>488</v>
+        <v>452</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>433</v>
+        <v>452</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12201,10 +12266,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>489</v>
+        <v>453</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>434</v>
+        <v>453</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12315,14 +12380,14 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>490</v>
+        <v>454</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>435</v>
+        <v>454</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>436</v>
+        <v>455</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -12344,10 +12409,10 @@
         <v>110</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>437</v>
+        <v>456</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>438</v>
+        <v>457</v>
       </c>
       <c r="N91" t="s" s="2">
         <v>113</v>
@@ -12402,7 +12467,7 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>439</v>
+        <v>458</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -12431,10 +12496,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>491</v>
+        <v>459</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>440</v>
+        <v>459</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12460,14 +12525,14 @@
         <v>209</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>441</v>
+        <v>460</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>442</v>
+        <v>461</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" t="s" s="2">
-        <v>443</v>
+        <v>462</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>78</v>
@@ -12516,7 +12581,7 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>440</v>
+        <v>459</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -12534,7 +12599,7 @@
         <v>78</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>444</v>
+        <v>463</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>78</v>
@@ -12545,10 +12610,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>492</v>
+        <v>464</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>445</v>
+        <v>464</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12574,10 +12639,10 @@
         <v>232</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>446</v>
+        <v>465</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>447</v>
+        <v>466</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -12607,10 +12672,10 @@
         <v>159</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>449</v>
+        <v>468</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>78</v>
@@ -12628,7 +12693,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>445</v>
+        <v>464</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>89</v>
@@ -12646,10 +12711,10 @@
         <v>78</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>431</v>
+        <v>450</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>450</v>
+        <v>469</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>78</v>
@@ -12657,7 +12722,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>470</v>
@@ -12683,16 +12748,18 @@
         <v>78</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>103</v>
+        <v>319</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>104</v>
+        <v>471</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>105</v>
+        <v>472</v>
       </c>
       <c r="N94" s="2"/>
-      <c r="O94" s="2"/>
+      <c r="O94" t="s" s="2">
+        <v>473</v>
+      </c>
       <c r="P94" t="s" s="2">
         <v>78</v>
       </c>
@@ -12740,7 +12807,7 @@
         <v>78</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>106</v>
+        <v>470</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -12752,16 +12819,16 @@
         <v>78</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>107</v>
+        <v>474</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>78</v>
+        <v>475</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>78</v>
@@ -12769,21 +12836,21 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>494</v>
+        <v>476</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>78</v>
@@ -12795,17 +12862,15 @@
         <v>78</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>110</v>
+        <v>327</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>111</v>
+        <v>477</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>478</v>
+      </c>
+      <c r="N95" s="2"/>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>78</v>
@@ -12842,37 +12907,37 @@
         <v>78</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC95" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>117</v>
+        <v>476</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>107</v>
+        <v>479</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>78</v>
@@ -12883,12 +12948,14 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>495</v>
+        <v>480</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="C96" s="2"/>
+        <v>444</v>
+      </c>
+      <c r="C96" t="s" s="2">
+        <v>481</v>
+      </c>
       <c r="D96" t="s" s="2">
         <v>78</v>
       </c>
@@ -12906,23 +12973,19 @@
         <v>78</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>147</v>
+        <v>445</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>243</v>
+        <v>482</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>447</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>78</v>
       </c>
@@ -12958,17 +13021,19 @@
         <v>78</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AC96" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>475</v>
+        <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>247</v>
+        <v>444</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -12983,13 +13048,13 @@
         <v>101</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>248</v>
+        <v>449</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>249</v>
+        <v>450</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>78</v>
+        <v>451</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>78</v>
@@ -12997,14 +13062,12 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>496</v>
+        <v>483</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="C97" t="s" s="2">
-        <v>497</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
         <v>78</v>
       </c>
@@ -13022,23 +13085,19 @@
         <v>78</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>147</v>
+        <v>103</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>498</v>
+        <v>104</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N97" s="2"/>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>78</v>
       </c>
@@ -13062,11 +13121,13 @@
         <v>78</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y97" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z97" t="s" s="2">
-        <v>499</v>
+        <v>78</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>78</v>
@@ -13084,25 +13145,25 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>247</v>
+        <v>106</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>249</v>
+        <v>107</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>78</v>
@@ -13113,23 +13174,21 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>500</v>
+        <v>484</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="C98" t="s" s="2">
-        <v>501</v>
-      </c>
+        <v>453</v>
+      </c>
+      <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>78</v>
@@ -13138,23 +13197,21 @@
         <v>78</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>147</v>
+        <v>110</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>502</v>
+        <v>111</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>244</v>
+        <v>112</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>78</v>
       </c>
@@ -13178,11 +13235,13 @@
         <v>78</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y98" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z98" t="s" s="2">
-        <v>503</v>
+        <v>78</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>78</v>
@@ -13200,7 +13259,7 @@
         <v>78</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>247</v>
+        <v>117</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -13212,13 +13271,13 @@
         <v>78</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>249</v>
+        <v>107</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>78</v>
@@ -13229,45 +13288,45 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>504</v>
+        <v>485</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>482</v>
+        <v>454</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>78</v>
+        <v>455</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J99" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>292</v>
+        <v>456</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>293</v>
+        <v>457</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>294</v>
+        <v>113</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>295</v>
+        <v>206</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>78</v>
@@ -13316,25 +13375,25 @@
         <v>78</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>296</v>
+        <v>458</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>297</v>
+        <v>78</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>298</v>
+        <v>192</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>78</v>
@@ -13345,10 +13404,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>505</v>
+        <v>486</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13359,7 +13418,7 @@
         <v>79</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>78</v>
@@ -13371,17 +13430,17 @@
         <v>78</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>319</v>
+        <v>209</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>78</v>
@@ -13430,13 +13489,13 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>78</v>
@@ -13448,10 +13507,10 @@
         <v>78</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>456</v>
+        <v>78</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>78</v>
@@ -13459,10 +13518,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>506</v>
+        <v>487</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13470,7 +13529,7 @@
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G101" t="s" s="2">
         <v>89</v>
@@ -13485,13 +13544,13 @@
         <v>78</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>327</v>
+        <v>232</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -13518,13 +13577,13 @@
         <v>78</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>78</v>
+        <v>467</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>78</v>
+        <v>468</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>78</v>
@@ -13542,10 +13601,10 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH101" t="s" s="2">
         <v>89</v>
@@ -13560,10 +13619,10 @@
         <v>78</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>78</v>
+        <v>469</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>78</v>
@@ -13571,14 +13630,12 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>507</v>
+        <v>488</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="C102" t="s" s="2">
-        <v>508</v>
-      </c>
+        <v>489</v>
+      </c>
+      <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
         <v>78</v>
       </c>
@@ -13587,7 +13644,7 @@
         <v>79</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>78</v>
@@ -13599,13 +13656,13 @@
         <v>78</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>426</v>
+        <v>103</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>509</v>
+        <v>104</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>428</v>
+        <v>105</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -13656,28 +13713,28 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>425</v>
+        <v>106</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>430</v>
+        <v>78</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>431</v>
+        <v>107</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>432</v>
+        <v>78</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>78</v>
@@ -13685,21 +13742,21 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>510</v>
+        <v>490</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>433</v>
+        <v>491</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>78</v>
@@ -13711,15 +13768,17 @@
         <v>78</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N103" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>78</v>
@@ -13756,31 +13815,31 @@
         <v>78</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC103" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>78</v>
@@ -13797,14 +13856,14 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>511</v>
+        <v>492</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>434</v>
+        <v>493</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -13820,21 +13879,23 @@
         <v>78</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>111</v>
+        <v>243</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>112</v>
+        <v>244</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O104" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="O104" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="P104" t="s" s="2">
         <v>78</v>
       </c>
@@ -13870,19 +13931,17 @@
         <v>78</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC104" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="AC104" s="2"/>
       <c r="AD104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>78</v>
+        <v>494</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>117</v>
+        <v>247</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -13894,13 +13953,13 @@
         <v>78</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>78</v>
+        <v>248</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>107</v>
+        <v>249</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>78</v>
@@ -13911,45 +13970,47 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>512</v>
+        <v>495</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="C105" s="2"/>
+        <v>493</v>
+      </c>
+      <c r="C105" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="D105" t="s" s="2">
-        <v>436</v>
+        <v>78</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I105" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J105" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>437</v>
+        <v>243</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>438</v>
+        <v>244</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>113</v>
+        <v>245</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>206</v>
+        <v>246</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>78</v>
@@ -13974,13 +14035,11 @@
         <v>78</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y105" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="Y105" s="2"/>
       <c r="Z105" t="s" s="2">
-        <v>78</v>
+        <v>497</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>78</v>
@@ -13998,7 +14057,7 @@
         <v>78</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>439</v>
+        <v>247</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -14010,13 +14069,13 @@
         <v>78</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>78</v>
+        <v>248</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>192</v>
+        <v>249</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>78</v>
@@ -14027,12 +14086,14 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>513</v>
+        <v>498</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="C106" s="2"/>
+        <v>493</v>
+      </c>
+      <c r="C106" t="s" s="2">
+        <v>481</v>
+      </c>
       <c r="D106" t="s" s="2">
         <v>78</v>
       </c>
@@ -14041,7 +14102,7 @@
         <v>79</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>78</v>
@@ -14050,20 +14111,22 @@
         <v>78</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>209</v>
+        <v>147</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>441</v>
+        <v>243</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N106" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="O106" t="s" s="2">
-        <v>443</v>
+        <v>246</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>78</v>
@@ -14088,13 +14151,11 @@
         <v>78</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y106" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="Y106" s="2"/>
       <c r="Z106" t="s" s="2">
-        <v>78</v>
+        <v>499</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>78</v>
@@ -14112,7 +14173,7 @@
         <v>78</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>440</v>
+        <v>247</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -14127,10 +14188,10 @@
         <v>101</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>78</v>
+        <v>248</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>444</v>
+        <v>249</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>78</v>
@@ -14141,10 +14202,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>514</v>
+        <v>500</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>445</v>
+        <v>501</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14152,7 +14213,7 @@
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G107" t="s" s="2">
         <v>89</v>
@@ -14164,19 +14225,23 @@
         <v>78</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>232</v>
+        <v>103</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>446</v>
+        <v>292</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N107" s="2"/>
-      <c r="O107" s="2"/>
+        <v>293</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="O107" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="P107" t="s" s="2">
         <v>78</v>
       </c>
@@ -14200,13 +14265,13 @@
         <v>78</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>448</v>
+        <v>78</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>449</v>
+        <v>78</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>78</v>
@@ -14224,10 +14289,10 @@
         <v>78</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>445</v>
+        <v>296</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH107" t="s" s="2">
         <v>89</v>
@@ -14239,13 +14304,13 @@
         <v>101</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>78</v>
+        <v>297</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>431</v>
+        <v>298</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>450</v>
+        <v>78</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>78</v>
@@ -14253,7 +14318,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>515</v>
+        <v>502</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>470</v>
@@ -14279,16 +14344,18 @@
         <v>78</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>103</v>
+        <v>319</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>104</v>
+        <v>471</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>105</v>
+        <v>472</v>
       </c>
       <c r="N108" s="2"/>
-      <c r="O108" s="2"/>
+      <c r="O108" t="s" s="2">
+        <v>473</v>
+      </c>
       <c r="P108" t="s" s="2">
         <v>78</v>
       </c>
@@ -14336,7 +14403,7 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>106</v>
+        <v>470</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
@@ -14348,16 +14415,16 @@
         <v>78</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>107</v>
+        <v>474</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>78</v>
+        <v>475</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>78</v>
@@ -14365,21 +14432,21 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>78</v>
@@ -14391,17 +14458,15 @@
         <v>78</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>110</v>
+        <v>327</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>111</v>
+        <v>477</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>478</v>
+      </c>
+      <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>78</v>
@@ -14438,37 +14503,37 @@
         <v>78</v>
       </c>
       <c r="AB109" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC109" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD109" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE109" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>117</v>
+        <v>476</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>107</v>
+        <v>479</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>78</v>
@@ -14479,12 +14544,14 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>517</v>
+        <v>504</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="C110" s="2"/>
+        <v>444</v>
+      </c>
+      <c r="C110" t="s" s="2">
+        <v>505</v>
+      </c>
       <c r="D110" t="s" s="2">
         <v>78</v>
       </c>
@@ -14493,7 +14560,7 @@
         <v>79</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>78</v>
@@ -14502,23 +14569,19 @@
         <v>78</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>147</v>
+        <v>445</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>243</v>
+        <v>506</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>447</v>
+      </c>
+      <c r="N110" s="2"/>
+      <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>78</v>
       </c>
@@ -14554,17 +14617,19 @@
         <v>78</v>
       </c>
       <c r="AB110" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AC110" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD110" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE110" t="s" s="2">
-        <v>475</v>
+        <v>78</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>247</v>
+        <v>444</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -14579,13 +14644,13 @@
         <v>101</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>248</v>
+        <v>449</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>249</v>
+        <v>450</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>78</v>
+        <v>451</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>78</v>
@@ -14593,14 +14658,12 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>518</v>
+        <v>507</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="C111" t="s" s="2">
-        <v>519</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
         <v>78</v>
       </c>
@@ -14618,23 +14681,19 @@
         <v>78</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>147</v>
+        <v>103</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>520</v>
+        <v>104</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N111" s="2"/>
+      <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>78</v>
       </c>
@@ -14658,11 +14717,13 @@
         <v>78</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y111" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z111" t="s" s="2">
-        <v>521</v>
+        <v>78</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>78</v>
@@ -14680,25 +14741,25 @@
         <v>78</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>247</v>
+        <v>106</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>249</v>
+        <v>107</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>78</v>
@@ -14709,23 +14770,21 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>522</v>
+        <v>508</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="C112" t="s" s="2">
-        <v>508</v>
-      </c>
+        <v>453</v>
+      </c>
+      <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>78</v>
@@ -14734,23 +14793,21 @@
         <v>78</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>147</v>
+        <v>110</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>523</v>
+        <v>111</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>244</v>
+        <v>112</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>78</v>
       </c>
@@ -14774,11 +14831,13 @@
         <v>78</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y112" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z112" t="s" s="2">
-        <v>524</v>
+        <v>78</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>78</v>
@@ -14796,7 +14855,7 @@
         <v>78</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>247</v>
+        <v>117</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -14808,13 +14867,13 @@
         <v>78</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>249</v>
+        <v>107</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>78</v>
@@ -14825,45 +14884,45 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>525</v>
+        <v>509</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>482</v>
+        <v>454</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>78</v>
+        <v>455</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I113" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J113" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>292</v>
+        <v>456</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>293</v>
+        <v>457</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>294</v>
+        <v>113</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>295</v>
+        <v>206</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>78</v>
@@ -14912,25 +14971,25 @@
         <v>78</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>296</v>
+        <v>458</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>297</v>
+        <v>78</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>298</v>
+        <v>192</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>78</v>
@@ -14941,10 +15000,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>526</v>
+        <v>510</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14955,7 +15014,7 @@
         <v>79</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>78</v>
@@ -14967,17 +15026,17 @@
         <v>78</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>319</v>
+        <v>209</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" t="s" s="2">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>78</v>
@@ -15026,13 +15085,13 @@
         <v>78</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>78</v>
@@ -15044,10 +15103,10 @@
         <v>78</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>456</v>
+        <v>78</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>78</v>
@@ -15055,10 +15114,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>527</v>
+        <v>511</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15066,7 +15125,7 @@
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G115" t="s" s="2">
         <v>89</v>
@@ -15081,13 +15140,13 @@
         <v>78</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>327</v>
+        <v>232</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -15114,13 +15173,13 @@
         <v>78</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>78</v>
+        <v>467</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>78</v>
+        <v>468</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>78</v>
@@ -15138,10 +15197,10 @@
         <v>78</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="AG115" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH115" t="s" s="2">
         <v>89</v>
@@ -15156,10 +15215,10 @@
         <v>78</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>78</v>
+        <v>469</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>78</v>
@@ -15167,10 +15226,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>528</v>
+        <v>512</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>528</v>
+        <v>489</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15181,7 +15240,7 @@
         <v>79</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>78</v>
@@ -15193,20 +15252,16 @@
         <v>78</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>232</v>
+        <v>103</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>529</v>
+        <v>104</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>532</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N116" s="2"/>
+      <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>78</v>
       </c>
@@ -15230,54 +15285,2568 @@
         <v>78</v>
       </c>
       <c r="X116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF116" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AG116" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH116" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL116" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AM116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN116" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="C117" s="2"/>
+      <c r="D117" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="E117" s="2"/>
+      <c r="F117" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K117" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O117" s="2"/>
+      <c r="P117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q117" s="2"/>
+      <c r="R117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AF117" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AG117" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ117" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AK117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL117" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AM117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN117" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="C118" s="2"/>
+      <c r="D118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E118" s="2"/>
+      <c r="F118" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J118" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K118" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L118" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="M118" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="O118" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="P118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q118" s="2"/>
+      <c r="R118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AC118" s="2"/>
+      <c r="AD118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AF118" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AG118" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ118" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK118" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AL118" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AM118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN118" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="C119" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="D119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E119" s="2"/>
+      <c r="F119" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G119" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J119" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K119" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L119" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="M119" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="O119" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="P119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q119" s="2"/>
+      <c r="R119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X119" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="Y119" s="2"/>
+      <c r="Z119" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AA119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF119" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AG119" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ119" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK119" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AL119" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AM119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN119" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="C120" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="D120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E120" s="2"/>
+      <c r="F120" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G120" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J120" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K120" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L120" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M120" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="O120" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="P120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q120" s="2"/>
+      <c r="R120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X120" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="Y120" s="2"/>
+      <c r="Z120" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF120" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AG120" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ120" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK120" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AL120" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AM120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN120" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="C121" s="2"/>
+      <c r="D121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E121" s="2"/>
+      <c r="F121" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G121" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J121" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K121" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L121" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="M121" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="O121" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="P121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q121" s="2"/>
+      <c r="R121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF121" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AG121" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH121" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ121" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK121" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AL121" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AM121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN121" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="C122" s="2"/>
+      <c r="D122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E122" s="2"/>
+      <c r="F122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G122" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K122" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="L122" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M122" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="N122" s="2"/>
+      <c r="O122" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="P122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q122" s="2"/>
+      <c r="R122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF122" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AG122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH122" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ122" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL122" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AM122" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AN122" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="C123" s="2"/>
+      <c r="D123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E123" s="2"/>
+      <c r="F123" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G123" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K123" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="L123" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M123" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="N123" s="2"/>
+      <c r="O123" s="2"/>
+      <c r="P123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q123" s="2"/>
+      <c r="R123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF123" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AG123" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH123" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ123" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL123" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AM123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN123" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="C124" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="D124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E124" s="2"/>
+      <c r="F124" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K124" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="L124" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="M124" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="N124" s="2"/>
+      <c r="O124" s="2"/>
+      <c r="P124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q124" s="2"/>
+      <c r="R124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF124" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AG124" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ124" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK124" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AL124" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AM124" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AN124" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="C125" s="2"/>
+      <c r="D125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E125" s="2"/>
+      <c r="F125" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G125" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K125" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L125" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="M125" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="N125" s="2"/>
+      <c r="O125" s="2"/>
+      <c r="P125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q125" s="2"/>
+      <c r="R125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF125" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AG125" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH125" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL125" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AM125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN125" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="C126" s="2"/>
+      <c r="D126" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="E126" s="2"/>
+      <c r="F126" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K126" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L126" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="M126" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="N126" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O126" s="2"/>
+      <c r="P126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q126" s="2"/>
+      <c r="R126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF126" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AG126" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ126" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AK126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL126" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AM126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN126" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="C127" s="2"/>
+      <c r="D127" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="E127" s="2"/>
+      <c r="F127" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I127" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J127" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K127" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L127" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M127" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="N127" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O127" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="P127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q127" s="2"/>
+      <c r="R127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF127" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AG127" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ127" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AK127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL127" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AM127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN127" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="C128" s="2"/>
+      <c r="D128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E128" s="2"/>
+      <c r="F128" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K128" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="L128" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M128" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="N128" s="2"/>
+      <c r="O128" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="P128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q128" s="2"/>
+      <c r="R128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF128" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AG128" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ128" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL128" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AM128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN128" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="C129" s="2"/>
+      <c r="D129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E129" s="2"/>
+      <c r="F129" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G129" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K129" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="L129" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M129" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="N129" s="2"/>
+      <c r="O129" s="2"/>
+      <c r="P129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q129" s="2"/>
+      <c r="R129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X129" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="Y129" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="Z129" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AA129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF129" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AG129" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH129" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ129" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL129" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AM129" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AN129" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="C130" s="2"/>
+      <c r="D130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E130" s="2"/>
+      <c r="F130" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G130" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K130" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L130" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="M130" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="N130" s="2"/>
+      <c r="O130" s="2"/>
+      <c r="P130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q130" s="2"/>
+      <c r="R130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF130" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AG130" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH130" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL130" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AM130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN130" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="C131" s="2"/>
+      <c r="D131" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="E131" s="2"/>
+      <c r="F131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K131" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L131" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="M131" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="N131" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O131" s="2"/>
+      <c r="P131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q131" s="2"/>
+      <c r="R131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB131" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AC131" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AD131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE131" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AF131" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AG131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ131" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AK131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL131" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AM131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN131" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="C132" s="2"/>
+      <c r="D132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E132" s="2"/>
+      <c r="F132" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J132" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K132" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L132" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="M132" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="N132" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="O132" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="P132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q132" s="2"/>
+      <c r="R132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB132" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AC132" s="2"/>
+      <c r="AD132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE132" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AF132" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AG132" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ132" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK132" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AL132" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AM132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN132" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="C133" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="D133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E133" s="2"/>
+      <c r="F133" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G133" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J133" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K133" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L133" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="M133" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="O133" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="P133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q133" s="2"/>
+      <c r="R133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X133" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="Y133" s="2"/>
+      <c r="Z133" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AA133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF133" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AG133" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ133" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK133" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AL133" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AM133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN133" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="C134" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="D134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E134" s="2"/>
+      <c r="F134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G134" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J134" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K134" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L134" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="M134" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="N134" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="O134" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="P134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q134" s="2"/>
+      <c r="R134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X134" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="Y134" s="2"/>
+      <c r="Z134" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="AA134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF134" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AG134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ134" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK134" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AL134" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AM134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN134" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="C135" s="2"/>
+      <c r="D135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E135" s="2"/>
+      <c r="F135" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G135" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J135" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K135" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L135" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="M135" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="N135" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="O135" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="P135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q135" s="2"/>
+      <c r="R135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF135" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AG135" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH135" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ135" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK135" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AL135" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AM135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN135" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="B136" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="C136" s="2"/>
+      <c r="D136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E136" s="2"/>
+      <c r="F136" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G136" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K136" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="L136" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M136" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="N136" s="2"/>
+      <c r="O136" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="P136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q136" s="2"/>
+      <c r="R136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF136" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AG136" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH136" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ136" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL136" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AM136" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AN136" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="C137" s="2"/>
+      <c r="D137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E137" s="2"/>
+      <c r="F137" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G137" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K137" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="L137" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M137" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="N137" s="2"/>
+      <c r="O137" s="2"/>
+      <c r="P137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q137" s="2"/>
+      <c r="R137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF137" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AG137" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH137" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ137" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL137" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AM137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN137" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="C138" s="2"/>
+      <c r="D138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E138" s="2"/>
+      <c r="F138" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K138" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="L138" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="M138" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="N138" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="O138" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="P138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q138" s="2"/>
+      <c r="R138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X138" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="Y116" t="s" s="2">
+      <c r="Y138" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="Z116" t="s" s="2">
+      <c r="Z138" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="AA116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF116" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="AG116" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH116" t="s" s="2">
+      <c r="AA138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF138" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AG138" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH138" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="AI116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ116" t="s" s="2">
+      <c r="AI138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ138" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AK116" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="AL116" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="AM116" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="AN116" t="s" s="2">
+      <c r="AK138" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AL138" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AM138" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AN138" t="s" s="2">
         <v>78</v>
       </c>
     </row>
